--- a/public/volunteer-roster/templates/school-canteen-roster.xlsx
+++ b/public/volunteer-roster/templates/school-canteen-roster.xlsx
@@ -75,12 +75,13 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <cols>
-    <col min="1" max="1" width="16" customWidth="1"/>
-    <col min="2" max="2" width="20" customWidth="1"/>
+    <col min="1" max="1" width="14" customWidth="1"/>
+    <col min="2" max="2" width="22" customWidth="1"/>
     <col min="3" max="3" width="26" customWidth="1"/>
     <col min="4" max="4" width="22" customWidth="1"/>
     <col min="5" max="5" width="16" customWidth="1"/>
     <col min="6" max="6" width="12" customWidth="1"/>
+    <col min="7" max="7" width="12" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -94,11 +95,12 @@
       <c r="D1" s="1"/>
       <c r="E1" s="1"/>
       <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
     </row>
     <row r="2">
       <c r="A2" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Two volunteers a day covers recess and lunch in most primary canteens. Add a third on the busiest day.</t>
+          <t xml:space="preserve">Offer all day first, because a split shift costs a handover mid-prep. Offer the split anyway, because it is what fills. Keep the ten minutes of overlap — it is the only reason the afternoon volunteer knows what is in the warmer.</t>
         </is>
       </c>
       <c r="B2" s="0"/>
@@ -106,6 +108,7 @@
       <c r="D2" s="0"/>
       <c r="E2" s="0"/>
       <c r="F2" s="0"/>
+      <c r="G2" s="0"/>
     </row>
     <row r="3">
       <c r="A3" s="0"/>
@@ -114,18 +117,19 @@
       <c r="D3" s="0"/>
       <c r="E3" s="0"/>
       <c r="F3" s="0"/>
+      <c r="G3" s="0"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
+          <t xml:space="preserve">Day</t>
+        </is>
+      </c>
+      <c r="B4" s="1" t="inlineStr">
+        <is>
           <t xml:space="preserve">Shift</t>
         </is>
       </c>
-      <c r="B4" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Time</t>
-        </is>
-      </c>
       <c r="C4" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Job</t>
@@ -143,7 +147,12 @@
       </c>
       <c r="F4" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Confirmed?</t>
+          <t xml:space="preserve">Signed in</t>
+        </is>
+      </c>
+      <c r="G4" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Signed out</t>
         </is>
       </c>
     </row>
@@ -155,177 +164,452 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9:00am – 1:30pm</t>
+          <t xml:space="preserve">Morning 9.10 – 11.50am</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prep and serving</t>
+          <t xml:space="preserve">Orders, prep, recess counter</t>
         </is>
       </c>
       <c r="D5" s="2"/>
       <c r="E5" s="2"/>
       <c r="F5" s="2"/>
+      <c r="G5" s="2"/>
     </row>
     <row r="6">
       <c r="A6" s="0"/>
-      <c r="B6" s="0"/>
+      <c r="B6" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Morning 9.10 – 11.50am</t>
+        </is>
+      </c>
       <c r="C6" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Serving and cleanup</t>
+          <t xml:space="preserve">Prep and recess counter</t>
         </is>
       </c>
       <c r="D6" s="0"/>
       <c r="E6" s="0"/>
       <c r="F6" s="0"/>
+      <c r="G6" s="0"/>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Tuesday</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">9:00am – 1:30pm</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Prep and serving</t>
-        </is>
-      </c>
-      <c r="D7" s="2"/>
-      <c r="E7" s="2"/>
-      <c r="F7" s="2"/>
+      <c r="A7" s="0"/>
+      <c r="B7" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Afternoon 11.40am – 2.00pm</t>
+        </is>
+      </c>
+      <c r="C7" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lunch bagging and counter</t>
+        </is>
+      </c>
+      <c r="D7" s="0"/>
+      <c r="E7" s="0"/>
+      <c r="F7" s="0"/>
+      <c r="G7" s="0"/>
     </row>
     <row r="8">
       <c r="A8" s="0"/>
-      <c r="B8" s="0"/>
+      <c r="B8" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Afternoon 11.40am – 2.00pm</t>
+        </is>
+      </c>
       <c r="C8" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Serving and cleanup</t>
+          <t xml:space="preserve">Counter, wash-up, clean-down</t>
         </is>
       </c>
       <c r="D8" s="0"/>
       <c r="E8" s="0"/>
       <c r="F8" s="0"/>
+      <c r="G8" s="0"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Wednesday</t>
+          <t xml:space="preserve">Tuesday</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9:00am – 1:30pm</t>
+          <t xml:space="preserve">Morning 9.10 – 11.50am</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prep and serving</t>
+          <t xml:space="preserve">Orders, prep, recess counter</t>
         </is>
       </c>
       <c r="D9" s="2"/>
       <c r="E9" s="2"/>
       <c r="F9" s="2"/>
+      <c r="G9" s="2"/>
     </row>
     <row r="10">
       <c r="A10" s="0"/>
-      <c r="B10" s="0"/>
+      <c r="B10" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Morning 9.10 – 11.50am</t>
+        </is>
+      </c>
       <c r="C10" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Serving and cleanup</t>
+          <t xml:space="preserve">Prep and recess counter</t>
         </is>
       </c>
       <c r="D10" s="0"/>
       <c r="E10" s="0"/>
       <c r="F10" s="0"/>
+      <c r="G10" s="0"/>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Thursday</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">9:00am – 1:30pm</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Prep and serving</t>
-        </is>
-      </c>
-      <c r="D11" s="2"/>
-      <c r="E11" s="2"/>
-      <c r="F11" s="2"/>
+      <c r="A11" s="0"/>
+      <c r="B11" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Afternoon 11.40am – 2.00pm</t>
+        </is>
+      </c>
+      <c r="C11" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lunch bagging and counter</t>
+        </is>
+      </c>
+      <c r="D11" s="0"/>
+      <c r="E11" s="0"/>
+      <c r="F11" s="0"/>
+      <c r="G11" s="0"/>
     </row>
     <row r="12">
       <c r="A12" s="0"/>
-      <c r="B12" s="0"/>
+      <c r="B12" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Afternoon 11.40am – 2.00pm</t>
+        </is>
+      </c>
       <c r="C12" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Serving and cleanup</t>
+          <t xml:space="preserve">Counter, wash-up, clean-down</t>
         </is>
       </c>
       <c r="D12" s="0"/>
       <c r="E12" s="0"/>
       <c r="F12" s="0"/>
+      <c r="G12" s="0"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Friday</t>
+          <t xml:space="preserve">Wednesday</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9:00am – 1:30pm</t>
+          <t xml:space="preserve">Morning 9.10 – 11.50am</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prep and serving</t>
+          <t xml:space="preserve">Orders, prep, recess counter</t>
         </is>
       </c>
       <c r="D13" s="2"/>
       <c r="E13" s="2"/>
       <c r="F13" s="2"/>
+      <c r="G13" s="2"/>
     </row>
     <row r="14">
       <c r="A14" s="0"/>
-      <c r="B14" s="0"/>
+      <c r="B14" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Morning 9.10 – 11.50am</t>
+        </is>
+      </c>
       <c r="C14" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Serving and cleanup</t>
+          <t xml:space="preserve">Prep and recess counter</t>
         </is>
       </c>
       <c r="D14" s="0"/>
       <c r="E14" s="0"/>
       <c r="F14" s="0"/>
+      <c r="G14" s="0"/>
     </row>
     <row r="15">
       <c r="A15" s="0"/>
-      <c r="B15" s="0"/>
-      <c r="C15" s="0"/>
+      <c r="B15" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Afternoon 11.40am – 2.00pm</t>
+        </is>
+      </c>
+      <c r="C15" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lunch bagging and counter</t>
+        </is>
+      </c>
       <c r="D15" s="0"/>
       <c r="E15" s="0"/>
       <c r="F15" s="0"/>
+      <c r="G15" s="0"/>
     </row>
     <row r="16">
-      <c r="A16" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Made with bitibybit.com/volunteer-roster/ — free, no accounts.</t>
-        </is>
-      </c>
-      <c r="B16" s="0"/>
-      <c r="C16" s="0"/>
+      <c r="A16" s="0"/>
+      <c r="B16" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Afternoon 11.40am – 2.00pm</t>
+        </is>
+      </c>
+      <c r="C16" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Counter, wash-up, clean-down</t>
+        </is>
+      </c>
       <c r="D16" s="0"/>
       <c r="E16" s="0"/>
       <c r="F16" s="0"/>
+      <c r="G16" s="0"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Thursday</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Morning 9.10 – 11.50am</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Orders, prep, recess counter</t>
+        </is>
+      </c>
+      <c r="D17" s="2"/>
+      <c r="E17" s="2"/>
+      <c r="F17" s="2"/>
+      <c r="G17" s="2"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="0"/>
+      <c r="B18" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Morning 9.10 – 11.50am</t>
+        </is>
+      </c>
+      <c r="C18" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Prep and recess counter</t>
+        </is>
+      </c>
+      <c r="D18" s="0"/>
+      <c r="E18" s="0"/>
+      <c r="F18" s="0"/>
+      <c r="G18" s="0"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="0"/>
+      <c r="B19" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Afternoon 11.40am – 2.00pm</t>
+        </is>
+      </c>
+      <c r="C19" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lunch bagging and counter</t>
+        </is>
+      </c>
+      <c r="D19" s="0"/>
+      <c r="E19" s="0"/>
+      <c r="F19" s="0"/>
+      <c r="G19" s="0"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="0"/>
+      <c r="B20" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Afternoon 11.40am – 2.00pm</t>
+        </is>
+      </c>
+      <c r="C20" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Counter, wash-up, clean-down</t>
+        </is>
+      </c>
+      <c r="D20" s="0"/>
+      <c r="E20" s="0"/>
+      <c r="F20" s="0"/>
+      <c r="G20" s="0"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Friday</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Morning 9.10 – 11.50am</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Orders, prep, recess counter</t>
+        </is>
+      </c>
+      <c r="D21" s="2"/>
+      <c r="E21" s="2"/>
+      <c r="F21" s="2"/>
+      <c r="G21" s="2"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="0"/>
+      <c r="B22" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Morning 9.10 – 11.50am</t>
+        </is>
+      </c>
+      <c r="C22" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Prep and recess counter</t>
+        </is>
+      </c>
+      <c r="D22" s="0"/>
+      <c r="E22" s="0"/>
+      <c r="F22" s="0"/>
+      <c r="G22" s="0"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="0"/>
+      <c r="B23" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Afternoon 11.40am – 2.00pm</t>
+        </is>
+      </c>
+      <c r="C23" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lunch bagging and counter</t>
+        </is>
+      </c>
+      <c r="D23" s="0"/>
+      <c r="E23" s="0"/>
+      <c r="F23" s="0"/>
+      <c r="G23" s="0"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="0"/>
+      <c r="B24" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Afternoon 11.40am – 2.00pm</t>
+        </is>
+      </c>
+      <c r="C24" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Counter, wash-up, clean-down</t>
+        </is>
+      </c>
+      <c r="D24" s="0"/>
+      <c r="E24" s="0"/>
+      <c r="F24" s="0"/>
+      <c r="G24" s="0"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="0"/>
+      <c r="B25" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bagging 12.30 – 2.30pm</t>
+        </is>
+      </c>
+      <c r="C25" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bagging and basket packing</t>
+        </is>
+      </c>
+      <c r="D25" s="0"/>
+      <c r="E25" s="0"/>
+      <c r="F25" s="0"/>
+      <c r="G25" s="0"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Any day</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">At home</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tea towels and aprons washed</t>
+        </is>
+      </c>
+      <c r="D26" s="2"/>
+      <c r="E26" s="2"/>
+      <c r="F26" s="2"/>
+      <c r="G26" s="2"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Reserves</t>
+        </is>
+      </c>
+      <c r="B27" s="2"/>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Named, not "ring around"</t>
+        </is>
+      </c>
+      <c r="D27" s="2"/>
+      <c r="E27" s="2"/>
+      <c r="F27" s="2"/>
+      <c r="G27" s="2"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="0"/>
+      <c r="B28" s="0"/>
+      <c r="C28" s="0"/>
+      <c r="D28" s="0"/>
+      <c r="E28" s="0"/>
+      <c r="F28" s="0"/>
+      <c r="G28" s="0"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="0"/>
+      <c r="B29" s="0"/>
+      <c r="C29" s="0"/>
+      <c r="D29" s="0"/>
+      <c r="E29" s="0"/>
+      <c r="F29" s="0"/>
+      <c r="G29" s="0"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="0"/>
+      <c r="B30" s="0"/>
+      <c r="C30" s="0"/>
+      <c r="D30" s="0"/>
+      <c r="E30" s="0"/>
+      <c r="F30" s="0"/>
+      <c r="G30" s="0"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Made with bitibybit.com/volunteer-roster/ — free, no accounts.</t>
+        </is>
+      </c>
+      <c r="B31" s="0"/>
+      <c r="C31" s="0"/>
+      <c r="D31" s="0"/>
+      <c r="E31" s="0"/>
+      <c r="F31" s="0"/>
+      <c r="G31" s="0"/>
     </row>
   </sheetData>
 </worksheet>
